--- a/servers/maze_main_server/conf.d/data/maze_equip_affix_order_v8【迷宫-装备-词条排序】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_equip_affix_order_v8【迷宫-装备-词条排序】.xlsx
@@ -1,41 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\新建文件夹\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8B13695-5B67-478C-BA93-4ADD4EFFC15E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="12860"/>
   </bookViews>
   <sheets>
     <sheet name="maze_equip_affix_order_v8" sheetId="1" r:id="rId1"/>
     <sheet name="备注" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_equip_affix_order_v8!$A$4:$A$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_equip_affix_order_v8!$A$4:$A$12</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="82">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -44,41 +27,107 @@
   </si>
   <si>
     <t>MAP&lt;INT:INT&gt;_S</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pos</t>
+  </si>
+  <si>
+    <t>attr_order</t>
   </si>
   <si>
     <t>装备部位类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pos</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>attr_order</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>属性id:排序</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10631:316_10632:315_10639:314_10640:313_10633:312_10634:311_10641:310_10642:309_10635:308_10636:307_10643:306_10644:305_10637:304_10638:303_10645:302_10646:301_10550:201_10525:113_10519:112_10520:111_10521:110_10522:109_10559:108_10625:107_10536:106_10537:105_10627:104_10626:103_10538:102_10582:101_10569:17_10568:16_10579:15_10572:14_10573:13_10574:12_10575:11_10577:10_10576:9_10571:8_10570:7_10578:6_10580:5_10551:4_10533:3_10534:2_10535:1</t>
   </si>
   <si>
     <t>排序</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击速度</t>
+  </si>
+  <si>
+    <t>暴击几率</t>
+  </si>
+  <si>
+    <t>移动速度</t>
   </si>
   <si>
     <t>火焰伤害</t>
   </si>
   <si>
+    <t>冰冷伤害</t>
+  </si>
+  <si>
     <t>闪电伤害</t>
   </si>
   <si>
     <t>毒伤害</t>
   </si>
   <si>
+    <t>火焰伤害提高</t>
+  </si>
+  <si>
+    <t>冰冷伤害提高</t>
+  </si>
+  <si>
+    <t>闪电伤害提高</t>
+  </si>
+  <si>
+    <t>毒伤害提高</t>
+  </si>
+  <si>
+    <t>额外火焰伤害</t>
+  </si>
+  <si>
+    <t>额外冰冷伤害</t>
+  </si>
+  <si>
+    <t>额外闪电伤害</t>
+  </si>
+  <si>
+    <t>额外毒伤害</t>
+  </si>
+  <si>
+    <t>火焰抗性</t>
+  </si>
+  <si>
     <t>冰冷抗性</t>
   </si>
   <si>
+    <t>闪电抗性</t>
+  </si>
+  <si>
+    <t>毒抗性</t>
+  </si>
+  <si>
+    <t>召唤兽持续时间提高</t>
+  </si>
+  <si>
+    <t>召唤冷却时间减少</t>
+  </si>
+  <si>
+    <t>洞察</t>
+  </si>
+  <si>
+    <t>反击伤害</t>
+  </si>
+  <si>
+    <t>反击时间</t>
+  </si>
+  <si>
+    <t>生命恢复效果</t>
+  </si>
+  <si>
+    <t>反伤</t>
+  </si>
+  <si>
+    <t>防御自爆</t>
+  </si>
+  <si>
     <t>复活时间减少</t>
   </si>
   <si>
@@ -94,175 +143,73 @@
     <t>1血不死</t>
   </si>
   <si>
-    <t>暴击几率</t>
-  </si>
-  <si>
-    <t>攻击速度</t>
-  </si>
-  <si>
-    <t>移动速度</t>
-  </si>
-  <si>
-    <t>冰冷伤害</t>
-  </si>
-  <si>
-    <t>火焰伤害提高</t>
-  </si>
-  <si>
-    <t>冰冷伤害提高</t>
-  </si>
-  <si>
-    <t>闪电伤害提高</t>
-  </si>
-  <si>
-    <t>毒伤害提高</t>
-  </si>
-  <si>
-    <t>额外火焰伤害</t>
-  </si>
-  <si>
-    <t>额外冰冷伤害</t>
-  </si>
-  <si>
-    <t>额外闪电伤害</t>
-  </si>
-  <si>
-    <t>额外毒伤害</t>
-  </si>
-  <si>
-    <t>火焰抗性</t>
-  </si>
-  <si>
-    <t>闪电抗性</t>
-  </si>
-  <si>
-    <t>毒抗性</t>
-  </si>
-  <si>
-    <t>召唤兽持续时间提高</t>
-  </si>
-  <si>
-    <t>召唤冷却时间减少</t>
-  </si>
-  <si>
-    <t>洞察</t>
-  </si>
-  <si>
-    <t>反击伤害</t>
-  </si>
-  <si>
-    <t>反击时间</t>
-  </si>
-  <si>
-    <t>生命恢复效果</t>
-  </si>
-  <si>
-    <t>反伤</t>
-  </si>
-  <si>
-    <t>防御自爆</t>
-  </si>
-  <si>
-    <t>暴击几率</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>全抗</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>血瓶生命回复效果</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>暴击伤害</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>移动速度</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>受到伤害时反伤</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>血瓶数量</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>复活</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>对精英怪伤害提高</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>对普通怪伤害提高</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>受到精英怪伤害减少</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>受到普通怪伤害减少</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>自己死亡时爆炸</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>击中敌人有概率击晕</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>精英掉装概率</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>受到电伤减少</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>受到毒伤减少</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>1血不死</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>击中回血</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>抵抗破甲诅咒</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>抵抗衰弱诅咒</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>闪避</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>技能[冰刺]等级</t>
   </si>
   <si>
     <t>中毒效果降低</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>技能[炎击]等级</t>
   </si>
   <si>
     <t>受到火伤减少</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>技能[寒霜爆]等级</t>
@@ -274,15 +221,16 @@
     <t>技能[铃兰]等级</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>技能[火流星]等级</t>
   </si>
   <si>
     <t>受到远程伤害减少</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>受到冰伤减少</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>技能[冰矛]等级</t>
@@ -298,7 +246,6 @@
   </si>
   <si>
     <t>受到近战伤害减少</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>技能[寒冰弹]等级</t>
@@ -317,19 +264,19 @@
   </si>
   <si>
     <t>技能[碧玉蛊]等级</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>10631:316_10632:315_10639:314_10640:313_10633:312_10634:311_10641:310_10642:309_10635:308_10636:307_10643:306_10644:305_10637:304_10638:303_10645:302_10646:301_10550:201_10525:113_10519:112_10520:111_10521:110_10522:109_10559:108_10625:107_10536:106_10537:105_10627:104_10626:103_10538:102_10582:101_10569:17_10568:16_10579:15_10572:14_10573:13_10574:12_10575:11_10577:10_10576:9_10571:8_10570:7_10578:6_10580:5_10551:4_10533:3_10534:2_10535:1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -337,56 +284,185 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <sz val="11"/>
+      <color theme="4" tint="-0.249977111117893"/>
+      <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="7" tint="-0.249977111117893"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="等线"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="4" tint="-0.249977111117893"/>
+      <color rgb="FF3F3F76"/>
       <name val="等线"/>
-      <family val="2"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="7" tint="-0.249977111117893"/>
+      <color rgb="FFFA7D00"/>
       <name val="等线"/>
-      <family val="2"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -395,47 +471,228 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.89999084444715716"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.899990844447157"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -458,64 +715,331 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="8" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="8" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="8" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="8" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="8" applyFont="1" applyAlignment="1" quotePrefix="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="注释" xfId="1" builtinId="10"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -793,138 +1317,140 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.5" customWidth="1"/>
+    <col min="2" max="2" width="18.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:1">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:2">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="14" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:2">
+      <c r="A3" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="4" t="s">
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="15" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A4" s="6" t="s">
+      <c r="B4" s="17" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="6">
+        <v>1</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="6">
+        <v>2</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="6">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B7" s="18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="6">
+        <v>4</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="6">
+        <v>5</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="6">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A5" s="1">
-        <v>1</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A6" s="1">
-        <v>2</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A7" s="1">
-        <v>3</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A8" s="1">
-        <v>4</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A9" s="1">
-        <v>5</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A10" s="1">
-        <v>6</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A11" s="1">
+      <c r="B10" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A12" s="1">
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="6">
+        <v>7</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="6">
         <v>8</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>84</v>
+      <c r="B12" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:A10" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <autoFilter ref="A4:A12">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FF5FED7-6609-405E-A1A7-381C3CDEBD32}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A6:P106"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="9" max="9" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="4:13" x14ac:dyDescent="0.15">
-      <c r="J6" s="8" t="s">
-        <v>7</v>
+    <row r="6" spans="10:11">
+      <c r="J6" s="10" t="s">
+        <v>8</v>
       </c>
       <c r="K6" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,K8:K39)</f>
         <v>10902:32_10901:31_11021:30_10101:29_10102:28_10103:27_10104:26_10111:25_10112:24_10113:23_10114:22_10115:21_10116:20_10117:19_10118:18_10119:17_10120:16_10121:15_10122:14_10123:13_10124:12_10125:11_10126:10_10127:9_10128:8_10129:7_10130:6_10131:5_10132:4_10133:3_10134:2_10135:1</v>
       </c>
     </row>
-    <row r="8" spans="4:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="8" spans="4:13">
       <c r="D8" t="e">
         <f>VLOOKUP(F11,#REF!,1,FALSE)</f>
         <v>#REF!</v>
@@ -933,20 +1459,20 @@
         <f>VLOOKUP(F11,#REF!,2,FALSE)</f>
         <v>#REF!</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="8">
         <v>10902</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="8">
         <v>1</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="8">
         <v>0</v>
       </c>
-      <c r="I8" s="7" t="s">
-        <v>18</v>
+      <c r="I8" s="8" t="s">
+        <v>9</v>
       </c>
       <c r="J8">
-        <f t="shared" ref="J8:J24" si="0">J9+1</f>
+        <f t="shared" ref="J8:J25" si="0">J9+1</f>
         <v>32</v>
       </c>
       <c r="K8" t="str">
@@ -957,7 +1483,7 @@
         <v>10101</v>
       </c>
     </row>
-    <row r="9" spans="4:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="9" spans="4:13">
       <c r="D9" t="e">
         <f>VLOOKUP(F12,#REF!,1,FALSE)</f>
         <v>#REF!</v>
@@ -966,17 +1492,17 @@
         <f>VLOOKUP(F12,#REF!,2,FALSE)</f>
         <v>#REF!</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="8">
         <v>10901</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="8">
         <v>1</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9" s="8">
         <v>0</v>
       </c>
-      <c r="I9" s="7" t="s">
-        <v>17</v>
+      <c r="I9" s="8" t="s">
+        <v>10</v>
       </c>
       <c r="J9">
         <f t="shared" si="0"/>
@@ -990,7 +1516,7 @@
         <v>10102</v>
       </c>
     </row>
-    <row r="10" spans="4:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="10" spans="4:13">
       <c r="D10" t="e">
         <f>VLOOKUP(F15,#REF!,1,FALSE)</f>
         <v>#REF!</v>
@@ -999,17 +1525,17 @@
         <f>VLOOKUP(F15,#REF!,2,FALSE)</f>
         <v>#REF!</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="8">
         <v>11021</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="8">
         <v>1</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="8">
         <v>0</v>
       </c>
-      <c r="I10" s="7" t="s">
-        <v>19</v>
+      <c r="I10" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="J10">
         <f t="shared" si="0"/>
@@ -1023,7 +1549,7 @@
         <v>10103</v>
       </c>
     </row>
-    <row r="11" spans="4:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="11" spans="4:13">
       <c r="D11" t="e">
         <f>VLOOKUP(F16,#REF!,1,FALSE)</f>
         <v>#REF!</v>
@@ -1032,17 +1558,17 @@
         <f>VLOOKUP(F16,#REF!,2,FALSE)</f>
         <v>#REF!</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="8">
         <v>10101</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="8">
         <v>1</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="8">
         <v>0</v>
       </c>
-      <c r="I11" s="7" t="s">
-        <v>8</v>
+      <c r="I11" s="8" t="s">
+        <v>12</v>
       </c>
       <c r="J11">
         <f t="shared" si="0"/>
@@ -1056,7 +1582,7 @@
         <v>10104</v>
       </c>
     </row>
-    <row r="12" spans="4:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="12" spans="4:11">
       <c r="D12" t="e">
         <f>VLOOKUP(F17,#REF!,1,FALSE)</f>
         <v>#REF!</v>
@@ -1065,17 +1591,17 @@
         <f>VLOOKUP(F17,#REF!,2,FALSE)</f>
         <v>#REF!</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="8">
         <v>10102</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="8">
         <v>1</v>
       </c>
-      <c r="H12" s="7">
+      <c r="H12" s="8">
         <v>0</v>
       </c>
-      <c r="I12" s="7" t="s">
-        <v>20</v>
+      <c r="I12" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="J12">
         <f t="shared" si="0"/>
@@ -1086,7 +1612,7 @@
         <v>10102:28</v>
       </c>
     </row>
-    <row r="13" spans="4:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="13" spans="4:11">
       <c r="D13" t="e">
         <f>VLOOKUP(F18,#REF!,1,FALSE)</f>
         <v>#REF!</v>
@@ -1095,17 +1621,17 @@
         <f>VLOOKUP(F18,#REF!,2,FALSE)</f>
         <v>#REF!</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="8">
         <v>10103</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="8">
         <v>1</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H13" s="8">
         <v>0</v>
       </c>
-      <c r="I13" s="7" t="s">
-        <v>9</v>
+      <c r="I13" s="8" t="s">
+        <v>14</v>
       </c>
       <c r="J13">
         <f t="shared" si="0"/>
@@ -1116,7 +1642,7 @@
         <v>10103:27</v>
       </c>
     </row>
-    <row r="14" spans="4:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="14" spans="4:11">
       <c r="D14" t="e">
         <f>VLOOKUP(F19,#REF!,1,FALSE)</f>
         <v>#REF!</v>
@@ -1125,17 +1651,17 @@
         <f>VLOOKUP(F19,#REF!,2,FALSE)</f>
         <v>#REF!</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="8">
         <v>10104</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="8">
         <v>1</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="8">
         <v>0</v>
       </c>
-      <c r="I14" s="7" t="s">
-        <v>10</v>
+      <c r="I14" s="8" t="s">
+        <v>15</v>
       </c>
       <c r="J14">
         <f t="shared" si="0"/>
@@ -1146,7 +1672,7 @@
         <v>10104:26</v>
       </c>
     </row>
-    <row r="15" spans="4:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="15" spans="4:11">
       <c r="D15" t="e">
         <f>VLOOKUP(F20,#REF!,1,FALSE)</f>
         <v>#REF!</v>
@@ -1155,17 +1681,17 @@
         <f>VLOOKUP(F20,#REF!,2,FALSE)</f>
         <v>#REF!</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="8">
         <v>10111</v>
       </c>
-      <c r="G15" s="7">
+      <c r="G15" s="8">
         <v>1</v>
       </c>
-      <c r="H15" s="7">
+      <c r="H15" s="8">
         <v>0</v>
       </c>
-      <c r="I15" s="7" t="s">
-        <v>21</v>
+      <c r="I15" s="8" t="s">
+        <v>16</v>
       </c>
       <c r="J15">
         <f t="shared" si="0"/>
@@ -1176,7 +1702,7 @@
         <v>10111:25</v>
       </c>
     </row>
-    <row r="16" spans="4:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="16" spans="4:11">
       <c r="D16" t="e">
         <f>VLOOKUP(F21,#REF!,1,FALSE)</f>
         <v>#REF!</v>
@@ -1185,17 +1711,17 @@
         <f>VLOOKUP(F21,#REF!,2,FALSE)</f>
         <v>#REF!</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="8">
         <v>10112</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="8">
         <v>1</v>
       </c>
-      <c r="H16" s="7">
+      <c r="H16" s="8">
         <v>0</v>
       </c>
-      <c r="I16" s="7" t="s">
-        <v>22</v>
+      <c r="I16" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="J16">
         <f t="shared" si="0"/>
@@ -1206,7 +1732,7 @@
         <v>10112:24</v>
       </c>
     </row>
-    <row r="17" spans="4:11" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="17" spans="4:11">
       <c r="D17" t="e">
         <f>VLOOKUP(F22,#REF!,1,FALSE)</f>
         <v>#REF!</v>
@@ -1215,17 +1741,17 @@
         <f>VLOOKUP(F22,#REF!,2,FALSE)</f>
         <v>#REF!</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="8">
         <v>10113</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G17" s="8">
         <v>1</v>
       </c>
-      <c r="H17" s="7">
+      <c r="H17" s="8">
         <v>0</v>
       </c>
-      <c r="I17" s="7" t="s">
-        <v>23</v>
+      <c r="I17" s="8" t="s">
+        <v>18</v>
       </c>
       <c r="J17">
         <f t="shared" si="0"/>
@@ -1236,7 +1762,7 @@
         <v>10113:23</v>
       </c>
     </row>
-    <row r="18" spans="4:11" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="18" spans="4:11">
       <c r="D18" t="e">
         <f>VLOOKUP(F8,#REF!,1,FALSE)</f>
         <v>#REF!</v>
@@ -1245,17 +1771,17 @@
         <f>VLOOKUP(F8,#REF!,2,FALSE)</f>
         <v>#REF!</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="8">
         <v>10114</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="8">
         <v>1</v>
       </c>
-      <c r="H18" s="7">
+      <c r="H18" s="8">
         <v>0</v>
       </c>
-      <c r="I18" s="7" t="s">
-        <v>24</v>
+      <c r="I18" s="8" t="s">
+        <v>19</v>
       </c>
       <c r="J18">
         <f t="shared" si="0"/>
@@ -1266,7 +1792,7 @@
         <v>10114:22</v>
       </c>
     </row>
-    <row r="19" spans="4:11" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="19" spans="4:11">
       <c r="D19" t="e">
         <f>VLOOKUP(F9,#REF!,1,FALSE)</f>
         <v>#REF!</v>
@@ -1275,17 +1801,17 @@
         <f>VLOOKUP(F9,#REF!,2,FALSE)</f>
         <v>#REF!</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="8">
         <v>10115</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G19" s="8">
         <v>1</v>
       </c>
-      <c r="H19" s="7">
+      <c r="H19" s="8">
         <v>0</v>
       </c>
-      <c r="I19" s="7" t="s">
-        <v>25</v>
+      <c r="I19" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="J19">
         <f t="shared" si="0"/>
@@ -1296,7 +1822,7 @@
         <v>10115:21</v>
       </c>
     </row>
-    <row r="20" spans="4:11" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="20" spans="4:11">
       <c r="D20" t="e">
         <f>VLOOKUP(F10,#REF!,1,FALSE)</f>
         <v>#REF!</v>
@@ -1305,17 +1831,17 @@
         <f>VLOOKUP(F10,#REF!,2,FALSE)</f>
         <v>#REF!</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20" s="8">
         <v>10116</v>
       </c>
-      <c r="G20" s="7">
+      <c r="G20" s="8">
         <v>1</v>
       </c>
-      <c r="H20" s="7">
+      <c r="H20" s="8">
         <v>0</v>
       </c>
-      <c r="I20" s="7" t="s">
-        <v>26</v>
+      <c r="I20" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="J20">
         <f t="shared" si="0"/>
@@ -1326,7 +1852,7 @@
         <v>10116:20</v>
       </c>
     </row>
-    <row r="21" spans="4:11" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="21" spans="4:11">
       <c r="D21" t="e">
         <f>VLOOKUP(F23,#REF!,1,FALSE)</f>
         <v>#REF!</v>
@@ -1335,17 +1861,17 @@
         <f>VLOOKUP(F23,#REF!,2,FALSE)</f>
         <v>#REF!</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F21" s="8">
         <v>10117</v>
       </c>
-      <c r="G21" s="7">
+      <c r="G21" s="8">
         <v>1</v>
       </c>
-      <c r="H21" s="7">
+      <c r="H21" s="8">
         <v>0</v>
       </c>
-      <c r="I21" s="7" t="s">
-        <v>27</v>
+      <c r="I21" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="J21">
         <f t="shared" si="0"/>
@@ -1356,7 +1882,7 @@
         <v>10117:19</v>
       </c>
     </row>
-    <row r="22" spans="4:11" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="22" spans="4:11">
       <c r="D22" t="e">
         <f>VLOOKUP(F24,#REF!,1,FALSE)</f>
         <v>#REF!</v>
@@ -1365,17 +1891,17 @@
         <f>VLOOKUP(F24,#REF!,2,FALSE)</f>
         <v>#REF!</v>
       </c>
-      <c r="F22" s="7">
+      <c r="F22" s="8">
         <v>10118</v>
       </c>
-      <c r="G22" s="7">
+      <c r="G22" s="8">
         <v>1</v>
       </c>
-      <c r="H22" s="7">
+      <c r="H22" s="8">
         <v>0</v>
       </c>
-      <c r="I22" s="7" t="s">
-        <v>28</v>
+      <c r="I22" s="8" t="s">
+        <v>23</v>
       </c>
       <c r="J22">
         <f t="shared" si="0"/>
@@ -1386,7 +1912,7 @@
         <v>10118:18</v>
       </c>
     </row>
-    <row r="23" spans="4:11" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="23" spans="4:11">
       <c r="D23" t="e">
         <f>VLOOKUP(F25,#REF!,1,FALSE)</f>
         <v>#REF!</v>
@@ -1395,17 +1921,17 @@
         <f>VLOOKUP(F25,#REF!,2,FALSE)</f>
         <v>#REF!</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F23" s="8">
         <v>10119</v>
       </c>
-      <c r="G23" s="7">
+      <c r="G23" s="8">
         <v>1</v>
       </c>
-      <c r="H23" s="7">
+      <c r="H23" s="8">
         <v>0</v>
       </c>
-      <c r="I23" s="7" t="s">
-        <v>29</v>
+      <c r="I23" s="8" t="s">
+        <v>24</v>
       </c>
       <c r="J23">
         <f t="shared" si="0"/>
@@ -1416,7 +1942,7 @@
         <v>10119:17</v>
       </c>
     </row>
-    <row r="24" spans="4:11" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="24" spans="4:11">
       <c r="D24" t="e">
         <f>VLOOKUP(F26,#REF!,1,FALSE)</f>
         <v>#REF!</v>
@@ -1425,17 +1951,17 @@
         <f>VLOOKUP(F26,#REF!,2,FALSE)</f>
         <v>#REF!</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F24" s="8">
         <v>10120</v>
       </c>
-      <c r="G24" s="7">
+      <c r="G24" s="8">
         <v>1</v>
       </c>
-      <c r="H24" s="7">
+      <c r="H24" s="8">
         <v>0</v>
       </c>
-      <c r="I24" s="7" t="s">
-        <v>11</v>
+      <c r="I24" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="J24">
         <f t="shared" si="0"/>
@@ -1446,21 +1972,21 @@
         <v>10120:16</v>
       </c>
     </row>
-    <row r="25" spans="4:11" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="F25" s="7">
+    <row r="25" spans="6:11">
+      <c r="F25" s="8">
         <v>10121</v>
       </c>
-      <c r="G25" s="7">
+      <c r="G25" s="8">
         <v>1</v>
       </c>
-      <c r="H25" s="7">
+      <c r="H25" s="8">
         <v>0</v>
       </c>
-      <c r="I25" s="7" t="s">
-        <v>30</v>
+      <c r="I25" s="8" t="s">
+        <v>26</v>
       </c>
       <c r="J25">
-        <f>J26+1</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="K25" t="str">
@@ -1468,18 +1994,18 @@
         <v>10121:15</v>
       </c>
     </row>
-    <row r="26" spans="4:11" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="F26" s="7">
+    <row r="26" spans="6:11">
+      <c r="F26" s="8">
         <v>10122</v>
       </c>
-      <c r="G26" s="7">
+      <c r="G26" s="8">
         <v>1</v>
       </c>
-      <c r="H26" s="7">
+      <c r="H26" s="8">
         <v>0</v>
       </c>
-      <c r="I26" s="7" t="s">
-        <v>31</v>
+      <c r="I26" s="8" t="s">
+        <v>27</v>
       </c>
       <c r="J26">
         <f t="shared" ref="J26:J39" si="2">J27+1</f>
@@ -1490,7 +2016,7 @@
         <v>10122:14</v>
       </c>
     </row>
-    <row r="27" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="27" spans="6:11">
       <c r="F27">
         <v>10123</v>
       </c>
@@ -1501,7 +2027,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="J27">
         <f t="shared" si="2"/>
@@ -1512,7 +2038,7 @@
         <v>10123:13</v>
       </c>
     </row>
-    <row r="28" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="28" spans="6:11">
       <c r="F28">
         <v>10124</v>
       </c>
@@ -1523,7 +2049,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="J28">
         <f t="shared" si="2"/>
@@ -1534,7 +2060,7 @@
         <v>10124:12</v>
       </c>
     </row>
-    <row r="29" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="29" spans="6:11">
       <c r="F29">
         <v>10125</v>
       </c>
@@ -1545,7 +2071,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J29">
         <f t="shared" si="2"/>
@@ -1556,7 +2082,7 @@
         <v>10125:11</v>
       </c>
     </row>
-    <row r="30" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="30" spans="6:11">
       <c r="F30">
         <v>10126</v>
       </c>
@@ -1567,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J30">
         <f t="shared" si="2"/>
@@ -1578,7 +2104,7 @@
         <v>10126:10</v>
       </c>
     </row>
-    <row r="31" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="31" spans="6:11">
       <c r="F31">
         <v>10127</v>
       </c>
@@ -1589,7 +2115,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="J31">
         <f t="shared" si="2"/>
@@ -1600,7 +2126,7 @@
         <v>10127:9</v>
       </c>
     </row>
-    <row r="32" spans="4:11" x14ac:dyDescent="0.15">
+    <row r="32" spans="6:11">
       <c r="F32">
         <v>10128</v>
       </c>
@@ -1611,7 +2137,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="J32">
         <f t="shared" si="2"/>
@@ -1622,7 +2148,7 @@
         <v>10128:8</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="33" spans="6:11">
       <c r="F33">
         <v>10129</v>
       </c>
@@ -1633,7 +2159,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="J33">
         <f t="shared" si="2"/>
@@ -1644,7 +2170,7 @@
         <v>10129:7</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="34" spans="6:11">
       <c r="F34">
         <v>10130</v>
       </c>
@@ -1655,7 +2181,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="J34">
         <f t="shared" si="2"/>
@@ -1666,7 +2192,7 @@
         <v>10130:6</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="35" spans="6:11">
       <c r="F35">
         <v>10131</v>
       </c>
@@ -1677,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="J35">
         <f t="shared" si="2"/>
@@ -1688,7 +2214,7 @@
         <v>10131:5</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="36" spans="6:11">
       <c r="F36">
         <v>10132</v>
       </c>
@@ -1699,7 +2225,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="J36">
         <f t="shared" si="2"/>
@@ -1710,7 +2236,7 @@
         <v>10132:4</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="37" spans="6:11">
       <c r="F37">
         <v>10133</v>
       </c>
@@ -1721,7 +2247,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="J37">
         <f t="shared" si="2"/>
@@ -1732,7 +2258,7 @@
         <v>10133:3</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="38" spans="6:11">
       <c r="F38">
         <v>10134</v>
       </c>
@@ -1743,7 +2269,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="J38">
         <f t="shared" si="2"/>
@@ -1754,7 +2280,7 @@
         <v>10134:2</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="39" spans="6:11">
       <c r="F39">
         <v>10135</v>
       </c>
@@ -1765,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J39">
         <f t="shared" si="2"/>
@@ -1776,7 +2302,7 @@
         <v>10135:1</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:16">
       <c r="A42">
         <v>1</v>
       </c>
@@ -1826,638 +2352,638 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A43" s="9" t="s">
+    <row r="43" spans="1:16">
+      <c r="A43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I43" s="11">
+        <v>10136</v>
+      </c>
+      <c r="J43" s="11">
+        <v>10125</v>
+      </c>
+      <c r="K43" s="11">
+        <v>10182</v>
+      </c>
+      <c r="L43" s="11">
+        <v>10125</v>
+      </c>
+      <c r="M43" s="11">
+        <v>10137</v>
+      </c>
+      <c r="N43" s="11">
+        <v>10138</v>
+      </c>
+      <c r="O43" s="11">
+        <v>10136</v>
+      </c>
+      <c r="P43" s="11">
+        <v>10136</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I44" s="11">
+        <v>10137</v>
+      </c>
+      <c r="J44" s="11">
+        <v>10119</v>
+      </c>
+      <c r="K44" s="11">
+        <v>10125</v>
+      </c>
+      <c r="L44" s="11">
+        <v>10119</v>
+      </c>
+      <c r="M44" s="12">
+        <v>10178</v>
+      </c>
+      <c r="N44" s="11">
+        <v>10137</v>
+      </c>
+      <c r="O44" s="11">
+        <v>10226</v>
+      </c>
+      <c r="P44" s="11">
+        <v>10227</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I45" s="12">
+        <v>10168</v>
+      </c>
+      <c r="J45" s="11">
+        <v>10120</v>
+      </c>
+      <c r="K45" s="11">
+        <v>10119</v>
+      </c>
+      <c r="L45" s="11">
+        <v>10120</v>
+      </c>
+      <c r="M45" s="12">
+        <v>10169</v>
+      </c>
+      <c r="N45" s="12">
+        <v>10170</v>
+      </c>
+      <c r="O45" s="12">
+        <v>10171</v>
+      </c>
+      <c r="P45" s="12">
+        <v>10180</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I46" s="12">
+        <v>10179</v>
+      </c>
+      <c r="J46" s="11">
+        <v>10121</v>
+      </c>
+      <c r="K46" s="11">
+        <v>10120</v>
+      </c>
+      <c r="L46" s="11">
+        <v>10121</v>
+      </c>
+      <c r="M46" s="13">
+        <v>10150</v>
+      </c>
+      <c r="N46" s="12">
+        <v>10174</v>
+      </c>
+      <c r="O46" s="12">
+        <v>10175</v>
+      </c>
+      <c r="P46" s="12">
+        <v>10178</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E47" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B43" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E43" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F43" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G43" s="9" t="s">
+      <c r="F47" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I47" s="13">
+        <v>10150</v>
+      </c>
+      <c r="J47" s="11">
+        <v>10122</v>
+      </c>
+      <c r="K47" s="11">
+        <v>10121</v>
+      </c>
+      <c r="L47" s="11">
+        <v>10122</v>
+      </c>
+      <c r="M47" s="12">
+        <v>10135</v>
+      </c>
+      <c r="N47" s="13">
+        <v>10150</v>
+      </c>
+      <c r="O47" s="13">
+        <v>10150</v>
+      </c>
+      <c r="P47" s="13">
+        <v>10150</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H43" s="9" t="s">
+      <c r="B48" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G48" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I43" s="15">
-        <v>10136</v>
-      </c>
-      <c r="J43" s="15">
-        <v>10125</v>
-      </c>
-      <c r="K43" s="15">
-        <v>10182</v>
-      </c>
-      <c r="L43" s="15">
-        <v>10125</v>
-      </c>
-      <c r="M43" s="15">
-        <v>10137</v>
-      </c>
-      <c r="N43" s="15">
-        <v>10138</v>
-      </c>
-      <c r="O43" s="15">
-        <v>10136</v>
-      </c>
-      <c r="P43" s="15">
-        <v>10136</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A44" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="B44" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E44" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="F44" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="G44" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="H44" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="I44" s="15">
-        <v>10137</v>
-      </c>
-      <c r="J44" s="15">
-        <v>10119</v>
-      </c>
-      <c r="K44" s="15">
-        <v>10125</v>
-      </c>
-      <c r="L44" s="15">
-        <v>10119</v>
-      </c>
-      <c r="M44" s="17">
-        <v>10178</v>
-      </c>
-      <c r="N44" s="15">
-        <v>10137</v>
-      </c>
-      <c r="O44" s="15">
-        <v>10226</v>
-      </c>
-      <c r="P44" s="15">
-        <v>10227</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A45" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="B45" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E45" s="10" t="s">
+      <c r="H48" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="I48" s="12">
+        <v>10135</v>
+      </c>
+      <c r="J48" s="11">
+        <v>10159</v>
+      </c>
+      <c r="K48" s="11">
+        <v>10122</v>
+      </c>
+      <c r="L48" s="11">
+        <v>10159</v>
+      </c>
+      <c r="M48" s="12">
+        <v>10151</v>
+      </c>
+      <c r="N48" s="12">
+        <v>10151</v>
+      </c>
+      <c r="O48" s="12">
+        <v>10135</v>
+      </c>
+      <c r="P48" s="12">
+        <v>10151</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16">
+      <c r="A49" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="H49" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="I49" s="12">
+        <v>10133</v>
+      </c>
+      <c r="J49" s="11">
+        <v>10225</v>
+      </c>
+      <c r="K49" s="11">
+        <v>10159</v>
+      </c>
+      <c r="L49" s="11">
+        <v>10225</v>
+      </c>
+      <c r="M49" s="9">
+        <v>10233</v>
+      </c>
+      <c r="N49" s="12">
+        <v>10134</v>
+      </c>
+      <c r="O49" s="12">
+        <v>10134</v>
+      </c>
+      <c r="P49" s="12">
+        <v>10133</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16">
+      <c r="A50" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H50" s="6"/>
+      <c r="I50" s="9">
+        <v>10231</v>
+      </c>
+      <c r="J50" s="12">
+        <v>10172</v>
+      </c>
+      <c r="K50" s="11">
+        <v>10225</v>
+      </c>
+      <c r="L50" s="12">
+        <v>10171</v>
+      </c>
+      <c r="M50" s="9">
+        <v>10234</v>
+      </c>
+      <c r="N50" s="9">
+        <v>10235</v>
+      </c>
+      <c r="O50" s="9">
+        <v>10237</v>
+      </c>
+      <c r="P50" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16">
+      <c r="A51" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="F45" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="G45" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="I45" s="17">
-        <v>10168</v>
-      </c>
-      <c r="J45" s="15">
-        <v>10120</v>
-      </c>
-      <c r="K45" s="15">
-        <v>10119</v>
-      </c>
-      <c r="L45" s="15">
-        <v>10120</v>
-      </c>
-      <c r="M45" s="17">
-        <v>10169</v>
-      </c>
-      <c r="N45" s="17">
+      <c r="D51" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="H51" s="6"/>
+      <c r="I51" s="9">
+        <v>10232</v>
+      </c>
+      <c r="J51" s="12">
+        <v>10177</v>
+      </c>
+      <c r="K51" s="12">
         <v>10170</v>
       </c>
-      <c r="O45" s="17">
-        <v>10171</v>
-      </c>
-      <c r="P45" s="17">
-        <v>10180</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A46" s="10" t="s">
+      <c r="L51" s="12">
+        <v>10173</v>
+      </c>
+      <c r="M51" s="9">
+        <v>10241</v>
+      </c>
+      <c r="N51" s="9">
+        <v>10236</v>
+      </c>
+      <c r="O51" s="9">
+        <v>10238</v>
+      </c>
+      <c r="P51" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16">
+      <c r="A52" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B46" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C46" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E46" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="F46" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="G46" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="H46" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="I46" s="17">
-        <v>10179</v>
-      </c>
-      <c r="J46" s="15">
-        <v>10121</v>
-      </c>
-      <c r="K46" s="15">
-        <v>10120</v>
-      </c>
-      <c r="L46" s="15">
-        <v>10121</v>
-      </c>
-      <c r="M46" s="18">
+      <c r="C52" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H52" s="6"/>
+      <c r="I52" s="9">
+        <v>10239</v>
+      </c>
+      <c r="J52" s="13">
         <v>10150</v>
       </c>
-      <c r="N46" s="17">
-        <v>10174</v>
-      </c>
-      <c r="O46" s="17">
-        <v>10175</v>
-      </c>
-      <c r="P46" s="17">
-        <v>10178</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A47" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="B47" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D47" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="E47" s="12" t="s">
+      <c r="K52" s="12">
+        <v>10176</v>
+      </c>
+      <c r="L52" s="13">
+        <v>10150</v>
+      </c>
+      <c r="M52" s="9">
+        <v>10242</v>
+      </c>
+      <c r="N52" s="9">
+        <v>10243</v>
+      </c>
+      <c r="O52" s="9">
+        <v>10245</v>
+      </c>
+      <c r="P52" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16">
+      <c r="A53" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D53" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F47" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="G47" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="H47" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="I47" s="18">
+      <c r="E53" s="6"/>
+      <c r="F53" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H53" s="6"/>
+      <c r="I53" s="9">
+        <v>10240</v>
+      </c>
+      <c r="J53" s="12">
+        <v>10133</v>
+      </c>
+      <c r="K53" s="13">
         <v>10150</v>
       </c>
-      <c r="J47" s="15">
-        <v>10122</v>
-      </c>
-      <c r="K47" s="15">
-        <v>10121</v>
-      </c>
-      <c r="L47" s="15">
-        <v>10122</v>
-      </c>
-      <c r="M47" s="17">
+      <c r="L53" s="12">
+        <v>10151</v>
+      </c>
+      <c r="M53" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="N53" s="9">
+        <v>10244</v>
+      </c>
+      <c r="O53" s="9">
+        <v>10246</v>
+      </c>
+      <c r="P53" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16">
+      <c r="A54" s="6"/>
+      <c r="B54" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E54" s="6"/>
+      <c r="F54" s="6"/>
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="J54" s="12">
+        <v>10134</v>
+      </c>
+      <c r="K54" s="12">
         <v>10135</v>
       </c>
-      <c r="N47" s="18">
-        <v>10150</v>
-      </c>
-      <c r="O47" s="18">
-        <v>10150</v>
-      </c>
-      <c r="P47" s="18">
-        <v>10150</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A48" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B48" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C48" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="E48" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="F48" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="G48" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="H48" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="I48" s="17">
-        <v>10135</v>
-      </c>
-      <c r="J48" s="15">
-        <v>10159</v>
-      </c>
-      <c r="K48" s="15">
-        <v>10122</v>
-      </c>
-      <c r="L48" s="15">
-        <v>10159</v>
-      </c>
-      <c r="M48" s="17">
-        <v>10151</v>
-      </c>
-      <c r="N48" s="17">
-        <v>10151</v>
-      </c>
-      <c r="O48" s="17">
-        <v>10135</v>
-      </c>
-      <c r="P48" s="17">
-        <v>10151</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A49" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="B49" s="9" t="s">
+      <c r="L54" s="12">
+        <v>10133</v>
+      </c>
+      <c r="M54" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="N54" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="O54" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="P54" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16">
+      <c r="A55" s="6"/>
+      <c r="B55" s="6"/>
+      <c r="C55" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C49" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="D49" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F49" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="G49" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="H49" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="I49" s="17">
-        <v>10133</v>
-      </c>
-      <c r="J49" s="15">
-        <v>10225</v>
-      </c>
-      <c r="K49" s="15">
-        <v>10159</v>
-      </c>
-      <c r="L49" s="15">
-        <v>10225</v>
-      </c>
-      <c r="M49" s="16">
-        <v>10233</v>
-      </c>
-      <c r="N49" s="17">
+      <c r="D55" s="6"/>
+      <c r="E55" s="6"/>
+      <c r="F55" s="6"/>
+      <c r="G55" s="6"/>
+      <c r="H55" s="6"/>
+      <c r="I55" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="J55" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="K55" s="12">
         <v>10134</v>
       </c>
-      <c r="O49" s="17">
-        <v>10134</v>
-      </c>
-      <c r="P49" s="17">
-        <v>10133</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A50" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B50" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C50" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D50" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F50" s="1" t="s">
+      <c r="L55" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="G50" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H50" s="1"/>
-      <c r="I50" s="16">
-        <v>10231</v>
-      </c>
-      <c r="J50" s="17">
-        <v>10172</v>
-      </c>
-      <c r="K50" s="15">
-        <v>10225</v>
-      </c>
-      <c r="L50" s="17">
-        <v>10171</v>
-      </c>
-      <c r="M50" s="16">
-        <v>10234</v>
-      </c>
-      <c r="N50" s="16">
-        <v>10235</v>
-      </c>
-      <c r="O50" s="16">
-        <v>10237</v>
-      </c>
-      <c r="P50" s="15" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A51" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B51" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C51" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D51" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="H51" s="1"/>
-      <c r="I51" s="16">
-        <v>10232</v>
-      </c>
-      <c r="J51" s="17">
-        <v>10177</v>
-      </c>
-      <c r="K51" s="17">
-        <v>10170</v>
-      </c>
-      <c r="L51" s="17">
-        <v>10173</v>
-      </c>
-      <c r="M51" s="16">
-        <v>10241</v>
-      </c>
-      <c r="N51" s="16">
-        <v>10236</v>
-      </c>
-      <c r="O51" s="16">
-        <v>10238</v>
-      </c>
-      <c r="P51" s="15" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A52" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B52" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C52" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="D52" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="H52" s="1"/>
-      <c r="I52" s="16">
-        <v>10239</v>
-      </c>
-      <c r="J52" s="18">
-        <v>10150</v>
-      </c>
-      <c r="K52" s="17">
-        <v>10176</v>
-      </c>
-      <c r="L52" s="18">
-        <v>10150</v>
-      </c>
-      <c r="M52" s="16">
-        <v>10242</v>
-      </c>
-      <c r="N52" s="16">
-        <v>10243</v>
-      </c>
-      <c r="O52" s="16">
-        <v>10245</v>
-      </c>
-      <c r="P52" s="15" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A53" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B53" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="C53" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="D53" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="E53" s="1"/>
-      <c r="F53" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="H53" s="1"/>
-      <c r="I53" s="16">
-        <v>10240</v>
-      </c>
-      <c r="J53" s="17">
-        <v>10133</v>
-      </c>
-      <c r="K53" s="18">
-        <v>10150</v>
-      </c>
-      <c r="L53" s="17">
-        <v>10151</v>
-      </c>
-      <c r="M53" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="N53" s="16">
-        <v>10244</v>
-      </c>
-      <c r="O53" s="16">
-        <v>10246</v>
-      </c>
-      <c r="P53" s="15" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A54" s="1"/>
-      <c r="B54" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="C54" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="D54" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
-      <c r="I54" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="J54" s="17">
-        <v>10134</v>
-      </c>
-      <c r="K54" s="17">
-        <v>10135</v>
-      </c>
-      <c r="L54" s="17">
-        <v>10133</v>
-      </c>
-      <c r="M54" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="N54" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="O54" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="P54" s="15" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A55" s="1"/>
-      <c r="B55" s="1"/>
-      <c r="C55" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="D55" s="1"/>
-      <c r="E55" s="1"/>
-      <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
-      <c r="H55" s="1"/>
-      <c r="I55" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="J55" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="K55" s="17">
-        <v>10134</v>
-      </c>
-      <c r="L55" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="M55" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="N55" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="O55" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="P55" s="15" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="M55" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="N55" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="O55" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="P55" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="59" spans="11:11">
       <c r="K59" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,K60:K106)</f>
         <v>10631:316_10632:315_10639:314_10640:313_10633:312_10634:311_10641:310_10642:309_10635:308_10636:307_10643:306_10644:305_10637:304_10638:303_10645:302_10646:301_10550:201_10525:113_10519:112_10520:111_10521:110_10522:109_10559:108_10625:107_10536:106_10537:105_10627:104_10626:103_10538:102_10582:101_10569:17_10568:16_10579:15_10572:14_10573:13_10574:12_10575:11_10577:10_10576:9_10571:8_10570:7_10578:6_10580:5_10551:4_10533:3_10534:2_10535:1</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="60" spans="7:11">
       <c r="G60">
         <f>H60+400</f>
         <v>10631</v>
       </c>
-      <c r="H60" s="16">
+      <c r="H60" s="9">
         <v>10231</v>
       </c>
-      <c r="I60" s="1" t="s">
-        <v>64</v>
+      <c r="I60" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="J60">
         <v>316</v>
@@ -2467,16 +2993,16 @@
         <v>10631:316</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="61" spans="7:11">
       <c r="G61">
         <f t="shared" ref="G61:G106" si="3">H61+400</f>
         <v>10632</v>
       </c>
-      <c r="H61" s="16">
+      <c r="H61" s="9">
         <v>10232</v>
       </c>
-      <c r="I61" s="1" t="s">
-        <v>69</v>
+      <c r="I61" s="6" t="s">
+        <v>68</v>
       </c>
       <c r="J61">
         <v>315</v>
@@ -2486,16 +3012,16 @@
         <v>10632:315</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="62" spans="7:11">
       <c r="G62">
         <f t="shared" si="3"/>
         <v>10639</v>
       </c>
-      <c r="H62" s="16">
+      <c r="H62" s="9">
         <v>10239</v>
       </c>
-      <c r="I62" s="1" t="s">
-        <v>75</v>
+      <c r="I62" s="6" t="s">
+        <v>74</v>
       </c>
       <c r="J62">
         <v>314</v>
@@ -2505,16 +3031,16 @@
         <v>10639:314</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="63" spans="7:11">
       <c r="G63">
         <f t="shared" si="3"/>
         <v>10640</v>
       </c>
-      <c r="H63" s="16">
+      <c r="H63" s="9">
         <v>10240</v>
       </c>
-      <c r="I63" s="1" t="s">
-        <v>80</v>
+      <c r="I63" s="6" t="s">
+        <v>79</v>
       </c>
       <c r="J63">
         <v>313</v>
@@ -2524,16 +3050,16 @@
         <v>10640:313</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="64" spans="7:11">
       <c r="G64">
         <f t="shared" si="3"/>
         <v>10633</v>
       </c>
-      <c r="H64" s="16">
+      <c r="H64" s="9">
         <v>10233</v>
       </c>
-      <c r="I64" s="1" t="s">
-        <v>62</v>
+      <c r="I64" s="6" t="s">
+        <v>60</v>
       </c>
       <c r="J64">
         <v>312</v>
@@ -2543,16 +3069,16 @@
         <v>10633:312</v>
       </c>
     </row>
-    <row r="65" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="65" spans="7:11">
       <c r="G65">
         <f t="shared" si="3"/>
         <v>10634</v>
       </c>
-      <c r="H65" s="16">
+      <c r="H65" s="9">
         <v>10234</v>
       </c>
-      <c r="I65" s="1" t="s">
-        <v>66</v>
+      <c r="I65" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="J65">
         <v>311</v>
@@ -2562,16 +3088,16 @@
         <v>10634:311</v>
       </c>
     </row>
-    <row r="66" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="66" spans="7:11">
       <c r="G66">
         <f t="shared" si="3"/>
         <v>10641</v>
       </c>
-      <c r="H66" s="16">
+      <c r="H66" s="9">
         <v>10241</v>
       </c>
-      <c r="I66" s="1" t="s">
-        <v>72</v>
+      <c r="I66" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="J66">
         <v>310</v>
@@ -2581,16 +3107,16 @@
         <v>10641:310</v>
       </c>
     </row>
-    <row r="67" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="67" spans="7:11">
       <c r="G67">
         <f t="shared" si="3"/>
         <v>10642</v>
       </c>
-      <c r="H67" s="16">
+      <c r="H67" s="9">
         <v>10242</v>
       </c>
-      <c r="I67" s="1" t="s">
-        <v>77</v>
+      <c r="I67" s="6" t="s">
+        <v>76</v>
       </c>
       <c r="J67">
         <v>309</v>
@@ -2600,16 +3126,16 @@
         <v>10642:309</v>
       </c>
     </row>
-    <row r="68" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="68" spans="7:11">
       <c r="G68">
         <f t="shared" si="3"/>
         <v>10635</v>
       </c>
-      <c r="H68" s="16">
+      <c r="H68" s="9">
         <v>10235</v>
       </c>
-      <c r="I68" s="1" t="s">
-        <v>67</v>
+      <c r="I68" s="6" t="s">
+        <v>65</v>
       </c>
       <c r="J68">
         <v>308</v>
@@ -2619,16 +3145,16 @@
         <v>10635:308</v>
       </c>
     </row>
-    <row r="69" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="69" spans="7:11">
       <c r="G69">
         <f t="shared" si="3"/>
         <v>10636</v>
       </c>
-      <c r="H69" s="16">
+      <c r="H69" s="9">
         <v>10236</v>
       </c>
-      <c r="I69" s="1" t="s">
-        <v>73</v>
+      <c r="I69" s="6" t="s">
+        <v>72</v>
       </c>
       <c r="J69">
         <v>307</v>
@@ -2638,16 +3164,16 @@
         <v>10636:307</v>
       </c>
     </row>
-    <row r="70" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="70" spans="7:11">
       <c r="G70">
         <f t="shared" si="3"/>
         <v>10643</v>
       </c>
-      <c r="H70" s="16">
+      <c r="H70" s="9">
         <v>10243</v>
       </c>
-      <c r="I70" s="1" t="s">
-        <v>78</v>
+      <c r="I70" s="6" t="s">
+        <v>77</v>
       </c>
       <c r="J70">
         <v>306</v>
@@ -2657,16 +3183,16 @@
         <v>10643:306</v>
       </c>
     </row>
-    <row r="71" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="71" spans="7:11">
       <c r="G71">
         <f t="shared" si="3"/>
         <v>10644</v>
       </c>
-      <c r="H71" s="16">
+      <c r="H71" s="9">
         <v>10244</v>
       </c>
-      <c r="I71" s="1" t="s">
-        <v>81</v>
+      <c r="I71" s="6" t="s">
+        <v>80</v>
       </c>
       <c r="J71">
         <v>305</v>
@@ -2676,16 +3202,16 @@
         <v>10644:305</v>
       </c>
     </row>
-    <row r="72" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="72" spans="7:11">
       <c r="G72">
         <f t="shared" si="3"/>
         <v>10637</v>
       </c>
-      <c r="H72" s="16">
+      <c r="H72" s="9">
         <v>10237</v>
       </c>
-      <c r="I72" s="1" t="s">
-        <v>68</v>
+      <c r="I72" s="6" t="s">
+        <v>66</v>
       </c>
       <c r="J72">
         <v>304</v>
@@ -2695,16 +3221,16 @@
         <v>10637:304</v>
       </c>
     </row>
-    <row r="73" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="73" spans="7:11">
       <c r="G73">
         <f t="shared" si="3"/>
         <v>10638</v>
       </c>
-      <c r="H73" s="16">
+      <c r="H73" s="9">
         <v>10238</v>
       </c>
-      <c r="I73" s="1" t="s">
-        <v>74</v>
+      <c r="I73" s="6" t="s">
+        <v>73</v>
       </c>
       <c r="J73">
         <v>303</v>
@@ -2714,16 +3240,16 @@
         <v>10638:303</v>
       </c>
     </row>
-    <row r="74" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="74" spans="7:11">
       <c r="G74">
         <f t="shared" si="3"/>
         <v>10645</v>
       </c>
-      <c r="H74" s="16">
+      <c r="H74" s="9">
         <v>10245</v>
       </c>
-      <c r="I74" s="1" t="s">
-        <v>79</v>
+      <c r="I74" s="6" t="s">
+        <v>78</v>
       </c>
       <c r="J74">
         <v>302</v>
@@ -2733,16 +3259,16 @@
         <v>10645:302</v>
       </c>
     </row>
-    <row r="75" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="75" spans="7:11">
       <c r="G75">
         <f t="shared" si="3"/>
         <v>10646</v>
       </c>
-      <c r="H75" s="16">
+      <c r="H75" s="9">
         <v>10246</v>
       </c>
-      <c r="I75" s="1" t="s">
-        <v>82</v>
+      <c r="I75" s="6" t="s">
+        <v>81</v>
       </c>
       <c r="J75">
         <v>301</v>
@@ -2752,16 +3278,16 @@
         <v>10646:301</v>
       </c>
     </row>
-    <row r="76" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="76" spans="7:11">
       <c r="G76">
         <f t="shared" si="3"/>
         <v>10550</v>
       </c>
-      <c r="H76" s="18">
+      <c r="H76" s="13">
         <v>10150</v>
       </c>
-      <c r="I76" s="18" t="s">
-        <v>54</v>
+      <c r="I76" s="13" t="s">
+        <v>53</v>
       </c>
       <c r="J76">
         <v>201</v>
@@ -2771,15 +3297,15 @@
         <v>10550:201</v>
       </c>
     </row>
-    <row r="77" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="77" spans="7:11">
       <c r="G77">
         <f t="shared" si="3"/>
         <v>10525</v>
       </c>
-      <c r="H77" s="15">
+      <c r="H77" s="11">
         <v>10125</v>
       </c>
-      <c r="I77" s="15" t="s">
+      <c r="I77" s="11" t="s">
         <v>41</v>
       </c>
       <c r="J77">
@@ -2790,16 +3316,16 @@
         <v>10525:113</v>
       </c>
     </row>
-    <row r="78" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="78" spans="7:11">
       <c r="G78">
         <f t="shared" si="3"/>
         <v>10519</v>
       </c>
-      <c r="H78" s="15">
+      <c r="H78" s="11">
         <v>10119</v>
       </c>
-      <c r="I78" s="15" t="s">
-        <v>29</v>
+      <c r="I78" s="11" t="s">
+        <v>24</v>
       </c>
       <c r="J78">
         <v>112</v>
@@ -2809,16 +3335,16 @@
         <v>10519:112</v>
       </c>
     </row>
-    <row r="79" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="79" spans="7:11">
       <c r="G79">
         <f t="shared" si="3"/>
         <v>10520</v>
       </c>
-      <c r="H79" s="15">
+      <c r="H79" s="11">
         <v>10120</v>
       </c>
-      <c r="I79" s="15" t="s">
-        <v>11</v>
+      <c r="I79" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="J79">
         <v>111</v>
@@ -2828,16 +3354,16 @@
         <v>10520:111</v>
       </c>
     </row>
-    <row r="80" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="80" spans="7:11">
       <c r="G80">
         <f t="shared" si="3"/>
         <v>10521</v>
       </c>
-      <c r="H80" s="15">
+      <c r="H80" s="11">
         <v>10121</v>
       </c>
-      <c r="I80" s="15" t="s">
-        <v>30</v>
+      <c r="I80" s="11" t="s">
+        <v>26</v>
       </c>
       <c r="J80">
         <v>110</v>
@@ -2847,16 +3373,16 @@
         <v>10521:110</v>
       </c>
     </row>
-    <row r="81" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="81" spans="7:11">
       <c r="G81">
         <f t="shared" si="3"/>
         <v>10522</v>
       </c>
-      <c r="H81" s="15">
+      <c r="H81" s="11">
         <v>10122</v>
       </c>
-      <c r="I81" s="15" t="s">
-        <v>31</v>
+      <c r="I81" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="J81">
         <v>109</v>
@@ -2866,16 +3392,16 @@
         <v>10522:109</v>
       </c>
     </row>
-    <row r="82" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="82" spans="7:11">
       <c r="G82">
         <f t="shared" si="3"/>
         <v>10559</v>
       </c>
-      <c r="H82" s="15">
+      <c r="H82" s="11">
         <v>10159</v>
       </c>
-      <c r="I82" s="15" t="s">
-        <v>58</v>
+      <c r="I82" s="11" t="s">
+        <v>56</v>
       </c>
       <c r="J82">
         <v>108</v>
@@ -2885,16 +3411,16 @@
         <v>10559:108</v>
       </c>
     </row>
-    <row r="83" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="83" spans="7:11">
       <c r="G83">
         <f t="shared" si="3"/>
         <v>10625</v>
       </c>
-      <c r="H83" s="15">
+      <c r="H83" s="11">
         <v>10225</v>
       </c>
-      <c r="I83" s="15" t="s">
-        <v>61</v>
+      <c r="I83" s="11" t="s">
+        <v>59</v>
       </c>
       <c r="J83">
         <v>107</v>
@@ -2904,16 +3430,16 @@
         <v>10625:107</v>
       </c>
     </row>
-    <row r="84" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="84" spans="7:11">
       <c r="G84">
         <f t="shared" si="3"/>
         <v>10536</v>
       </c>
-      <c r="H84" s="15">
+      <c r="H84" s="11">
         <v>10136</v>
       </c>
-      <c r="I84" s="15" t="s">
-        <v>40</v>
+      <c r="I84" s="11" t="s">
+        <v>10</v>
       </c>
       <c r="J84">
         <v>106</v>
@@ -2923,15 +3449,15 @@
         <v>10536:106</v>
       </c>
     </row>
-    <row r="85" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="85" spans="7:11">
       <c r="G85">
         <f t="shared" si="3"/>
         <v>10537</v>
       </c>
-      <c r="H85" s="15">
+      <c r="H85" s="11">
         <v>10137</v>
       </c>
-      <c r="I85" s="15" t="s">
+      <c r="I85" s="11" t="s">
         <v>43</v>
       </c>
       <c r="J85">
@@ -2942,16 +3468,16 @@
         <v>10537:105</v>
       </c>
     </row>
-    <row r="86" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="86" spans="7:11">
       <c r="G86">
         <f t="shared" si="3"/>
         <v>10627</v>
       </c>
-      <c r="H86" s="15">
+      <c r="H86" s="11">
         <v>10227</v>
       </c>
-      <c r="I86" s="15" t="s">
-        <v>47</v>
+      <c r="I86" s="11" t="s">
+        <v>46</v>
       </c>
       <c r="J86">
         <v>104</v>
@@ -2961,16 +3487,16 @@
         <v>10627:104</v>
       </c>
     </row>
-    <row r="87" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="87" spans="7:11">
       <c r="G87">
         <f t="shared" si="3"/>
         <v>10626</v>
       </c>
-      <c r="H87" s="15">
+      <c r="H87" s="11">
         <v>10226</v>
       </c>
-      <c r="I87" s="15" t="s">
-        <v>46</v>
+      <c r="I87" s="11" t="s">
+        <v>45</v>
       </c>
       <c r="J87">
         <v>103</v>
@@ -2980,16 +3506,16 @@
         <v>10626:103</v>
       </c>
     </row>
-    <row r="88" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="88" spans="7:11">
       <c r="G88">
         <f t="shared" si="3"/>
         <v>10538</v>
       </c>
-      <c r="H88" s="15">
+      <c r="H88" s="11">
         <v>10138</v>
       </c>
-      <c r="I88" s="15" t="s">
-        <v>44</v>
+      <c r="I88" s="11" t="s">
+        <v>11</v>
       </c>
       <c r="J88">
         <v>102</v>
@@ -2999,15 +3525,15 @@
         <v>10538:102</v>
       </c>
     </row>
-    <row r="89" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="89" spans="7:11">
       <c r="G89">
         <f t="shared" si="3"/>
         <v>10582</v>
       </c>
-      <c r="H89" s="15">
+      <c r="H89" s="11">
         <v>10182</v>
       </c>
-      <c r="I89" s="15" t="s">
+      <c r="I89" s="11" t="s">
         <v>42</v>
       </c>
       <c r="J89">
@@ -3018,16 +3544,16 @@
         <v>10582:101</v>
       </c>
     </row>
-    <row r="90" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="90" spans="7:11">
       <c r="G90">
         <f t="shared" si="3"/>
         <v>10569</v>
       </c>
-      <c r="H90" s="10">
+      <c r="H90" s="2">
         <v>10169</v>
       </c>
-      <c r="I90" s="10" t="s">
-        <v>49</v>
+      <c r="I90" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="J90">
         <v>17</v>
@@ -3037,16 +3563,16 @@
         <v>10569:17</v>
       </c>
     </row>
-    <row r="91" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="91" spans="7:11">
       <c r="G91">
         <f t="shared" si="3"/>
         <v>10568</v>
       </c>
-      <c r="H91" s="10">
+      <c r="H91" s="2">
         <v>10168</v>
       </c>
-      <c r="I91" s="10" t="s">
-        <v>48</v>
+      <c r="I91" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="J91">
         <v>16</v>
@@ -3056,16 +3582,16 @@
         <v>10568:16</v>
       </c>
     </row>
-    <row r="92" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="92" spans="7:11">
       <c r="G92">
         <f t="shared" si="3"/>
         <v>10579</v>
       </c>
-      <c r="H92" s="10">
+      <c r="H92" s="2">
         <v>10179</v>
       </c>
-      <c r="I92" s="10" t="s">
-        <v>53</v>
+      <c r="I92" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="J92">
         <v>15</v>
@@ -3075,16 +3601,16 @@
         <v>10579:15</v>
       </c>
     </row>
-    <row r="93" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="93" spans="7:11">
       <c r="G93">
         <f t="shared" si="3"/>
         <v>10572</v>
       </c>
-      <c r="H93" s="10">
+      <c r="H93" s="2">
         <v>10172</v>
       </c>
-      <c r="I93" s="10" t="s">
-        <v>65</v>
+      <c r="I93" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="J93">
         <v>14</v>
@@ -3094,16 +3620,16 @@
         <v>10572:14</v>
       </c>
     </row>
-    <row r="94" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="94" spans="7:11">
       <c r="G94">
         <f t="shared" si="3"/>
         <v>10573</v>
       </c>
-      <c r="H94" s="10">
+      <c r="H94" s="2">
         <v>10173</v>
       </c>
-      <c r="I94" s="10" t="s">
-        <v>71</v>
+      <c r="I94" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="J94">
         <v>13</v>
@@ -3113,16 +3639,16 @@
         <v>10573:13</v>
       </c>
     </row>
-    <row r="95" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="95" spans="7:11">
       <c r="G95">
         <f t="shared" si="3"/>
         <v>10574</v>
       </c>
-      <c r="H95" s="10">
+      <c r="H95" s="2">
         <v>10174</v>
       </c>
-      <c r="I95" s="10" t="s">
-        <v>55</v>
+      <c r="I95" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="J95">
         <v>12</v>
@@ -3132,16 +3658,16 @@
         <v>10574:12</v>
       </c>
     </row>
-    <row r="96" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="96" spans="7:11">
       <c r="G96">
         <f t="shared" si="3"/>
         <v>10575</v>
       </c>
-      <c r="H96" s="10">
+      <c r="H96" s="2">
         <v>10175</v>
       </c>
-      <c r="I96" s="10" t="s">
-        <v>56</v>
+      <c r="I96" s="2" t="s">
+        <v>55</v>
       </c>
       <c r="J96">
         <v>11</v>
@@ -3151,16 +3677,16 @@
         <v>10575:11</v>
       </c>
     </row>
-    <row r="97" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="97" spans="7:11">
       <c r="G97">
         <f t="shared" si="3"/>
         <v>10577</v>
       </c>
-      <c r="H97" s="10">
+      <c r="H97" s="2">
         <v>10177</v>
       </c>
-      <c r="I97" s="10" t="s">
-        <v>70</v>
+      <c r="I97" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="J97">
         <v>10</v>
@@ -3170,16 +3696,16 @@
         <v>10577:10</v>
       </c>
     </row>
-    <row r="98" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="98" spans="7:11">
       <c r="G98">
         <f t="shared" si="3"/>
         <v>10576</v>
       </c>
-      <c r="H98" s="10">
+      <c r="H98" s="2">
         <v>10176</v>
       </c>
-      <c r="I98" s="10" t="s">
-        <v>76</v>
+      <c r="I98" s="2" t="s">
+        <v>75</v>
       </c>
       <c r="J98">
         <v>9</v>
@@ -3189,16 +3715,16 @@
         <v>10576:9</v>
       </c>
     </row>
-    <row r="99" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="99" spans="7:11">
       <c r="G99">
         <f t="shared" si="3"/>
         <v>10571</v>
       </c>
-      <c r="H99" s="10">
+      <c r="H99" s="2">
         <v>10171</v>
       </c>
-      <c r="I99" s="10" t="s">
-        <v>51</v>
+      <c r="I99" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="J99">
         <v>8</v>
@@ -3208,16 +3734,16 @@
         <v>10571:8</v>
       </c>
     </row>
-    <row r="100" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="100" spans="7:11">
       <c r="G100">
         <f t="shared" si="3"/>
         <v>10570</v>
       </c>
-      <c r="H100" s="10">
+      <c r="H100" s="2">
         <v>10170</v>
       </c>
-      <c r="I100" s="10" t="s">
-        <v>50</v>
+      <c r="I100" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="J100">
         <v>7</v>
@@ -3227,16 +3753,16 @@
         <v>10570:7</v>
       </c>
     </row>
-    <row r="101" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="101" spans="7:11">
       <c r="G101">
         <f t="shared" si="3"/>
         <v>10578</v>
       </c>
-      <c r="H101" s="10">
+      <c r="H101" s="2">
         <v>10178</v>
       </c>
-      <c r="I101" s="10" t="s">
-        <v>45</v>
+      <c r="I101" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="J101">
         <v>6</v>
@@ -3246,16 +3772,16 @@
         <v>10578:6</v>
       </c>
     </row>
-    <row r="102" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="102" spans="7:11">
       <c r="G102">
         <f t="shared" si="3"/>
         <v>10580</v>
       </c>
-      <c r="H102" s="10">
+      <c r="H102" s="2">
         <v>10180</v>
       </c>
-      <c r="I102" s="10" t="s">
-        <v>52</v>
+      <c r="I102" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="J102">
         <v>5</v>
@@ -3265,16 +3791,16 @@
         <v>10580:5</v>
       </c>
     </row>
-    <row r="103" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="103" spans="7:11">
       <c r="G103">
         <f t="shared" si="3"/>
         <v>10551</v>
       </c>
-      <c r="H103" s="13">
+      <c r="H103" s="5">
         <v>10151</v>
       </c>
-      <c r="I103" s="13" t="s">
-        <v>59</v>
+      <c r="I103" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="J103">
         <v>4</v>
@@ -3284,16 +3810,16 @@
         <v>10551:4</v>
       </c>
     </row>
-    <row r="104" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="104" spans="7:11">
       <c r="G104">
         <f t="shared" si="3"/>
         <v>10533</v>
       </c>
-      <c r="H104" s="13">
+      <c r="H104" s="5">
         <v>10133</v>
       </c>
-      <c r="I104" s="13" t="s">
-        <v>60</v>
+      <c r="I104" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="J104">
         <v>3</v>
@@ -3303,16 +3829,16 @@
         <v>10533:3</v>
       </c>
     </row>
-    <row r="105" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="105" spans="7:11">
       <c r="G105">
         <f t="shared" si="3"/>
         <v>10534</v>
       </c>
-      <c r="H105" s="13">
+      <c r="H105" s="5">
         <v>10134</v>
       </c>
-      <c r="I105" s="13" t="s">
-        <v>63</v>
+      <c r="I105" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="J105">
         <v>2</v>
@@ -3322,16 +3848,16 @@
         <v>10534:2</v>
       </c>
     </row>
-    <row r="106" spans="7:11" x14ac:dyDescent="0.15">
+    <row r="106" spans="7:11">
       <c r="G106">
         <f t="shared" si="3"/>
         <v>10535</v>
       </c>
-      <c r="H106" s="13">
+      <c r="H106" s="5">
         <v>10135</v>
       </c>
-      <c r="I106" s="13" t="s">
-        <v>16</v>
+      <c r="I106" s="5" t="s">
+        <v>40</v>
       </c>
       <c r="J106">
         <v>1</v>
@@ -3342,7 +3868,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>